--- a/data/trans_orig/IP05A01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP05A01-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45754</t>
+          <t>44921</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61936</t>
+          <t>61284</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44447</t>
+          <t>43523</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60109</t>
+          <t>59114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94008</t>
+          <t>93257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116256</t>
+          <t>116116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>46099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>29870</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43993</t>
+          <t>44673</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63782</t>
+          <t>63515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85428</t>
+          <t>84881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20422</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>15661</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16299</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30785</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54103</t>
+          <t>54296</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32135</t>
+          <t>32290</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46971</t>
+          <t>47283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75525</t>
+          <t>75974</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>96761</t>
+          <t>96617</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,95%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26899</t>
+          <t>27044</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41905</t>
+          <t>41294</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>28586</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43499</t>
+          <t>42485</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>58882</t>
+          <t>58807</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15055</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23917</t>
+          <t>23106</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24946</t>
+          <t>24012</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37336</t>
+          <t>38347</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43896</t>
+          <t>43613</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59502</t>
+          <t>60326</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>72766</t>
+          <t>71931</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>92434</t>
+          <t>92390</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,64%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>21547</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34353</t>
+          <t>34472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30278</t>
+          <t>30113</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45005</t>
+          <t>45445</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>55836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75871</t>
+          <t>76528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13666</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>12467</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25488</t>
+          <t>25568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88382</t>
+          <t>88768</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110972</t>
+          <t>111258</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94262</t>
+          <t>92952</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116357</t>
+          <t>116505</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>189535</t>
+          <t>187511</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>220742</t>
+          <t>221315</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67489</t>
+          <t>66248</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90287</t>
+          <t>88258</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67705</t>
+          <t>67247</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90202</t>
+          <t>89151</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>139127</t>
+          <t>139515</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171527</t>
+          <t>171948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16789</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30839</t>
+          <t>31703</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27490</t>
+          <t>27354</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33516</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>53747</t>
+          <t>52866</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42928</t>
+          <t>43330</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59684</t>
+          <t>59385</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55137</t>
+          <t>53999</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73767</t>
+          <t>73180</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102790</t>
+          <t>102889</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127432</t>
+          <t>127083</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,21%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33851</t>
+          <t>33387</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50938</t>
+          <t>49219</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42684</t>
+          <t>42013</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59847</t>
+          <t>60370</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>82651</t>
+          <t>80454</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>105786</t>
+          <t>105427</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14956</t>
+          <t>15810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29758</t>
+          <t>29842</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>25824</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39520</t>
+          <t>39218</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24570</t>
+          <t>24803</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38087</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>54781</t>
+          <t>55559</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>73675</t>
+          <t>73985</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,24%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25745</t>
+          <t>26297</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39515</t>
+          <t>40475</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24138</t>
+          <t>23941</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37677</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53460</t>
+          <t>53198</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71923</t>
+          <t>72136</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,98%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>15301</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>16030</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>13706</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27792</t>
+          <t>27806</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>294634</t>
+          <t>294854</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>334778</t>
+          <t>336385</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>321998</t>
+          <t>322878</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>364318</t>
+          <t>364251</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>630576</t>
+          <t>626785</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>687924</t>
+          <t>688157</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>232163</t>
+          <t>231687</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>270284</t>
+          <t>271822</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>247689</t>
+          <t>249205</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>289748</t>
+          <t>288096</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>490523</t>
+          <t>492552</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>546421</t>
+          <t>549319</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>58938</t>
+          <t>60015</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>84561</t>
+          <t>85683</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58144</t>
+          <t>58860</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>84295</t>
+          <t>84515</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>125529</t>
+          <t>125428</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>161177</t>
+          <t>160747</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47225</t>
+          <t>46990</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61864</t>
+          <t>62201</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52021</t>
+          <t>50930</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66481</t>
+          <t>65673</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103325</t>
+          <t>102965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125048</t>
+          <t>123535</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19957</t>
+          <t>19927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33945</t>
+          <t>33821</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16948</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29777</t>
+          <t>30232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39940</t>
+          <t>39679</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60571</t>
+          <t>59353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23356</t>
+          <t>23503</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54577</t>
+          <t>53453</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69104</t>
+          <t>68903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56938</t>
+          <t>56917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72128</t>
+          <t>72041</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>116074</t>
+          <t>116165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>137468</t>
+          <t>137845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,53%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>19347</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32762</t>
+          <t>33650</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20107</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35285</t>
+          <t>35185</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43547</t>
+          <t>42550</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>63884</t>
+          <t>63516</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16362</t>
+          <t>15439</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52348</t>
+          <t>52030</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65934</t>
+          <t>65879</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63376</t>
+          <t>62830</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74970</t>
+          <t>74825</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>118900</t>
+          <t>120155</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>138087</t>
+          <t>137701</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,85%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14426</t>
+          <t>13980</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27121</t>
+          <t>26334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19837</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24715</t>
+          <t>25469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42314</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>16851</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>131981</t>
+          <t>133616</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154528</t>
+          <t>154656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>147463</t>
+          <t>146739</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>171290</t>
+          <t>171834</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>287592</t>
+          <t>288166</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>319371</t>
+          <t>319266</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,66%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37328</t>
+          <t>36968</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57744</t>
+          <t>55706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43601</t>
+          <t>43500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65871</t>
+          <t>65779</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>87190</t>
+          <t>86932</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>115529</t>
+          <t>116782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>22295</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>21644</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21073</t>
+          <t>21811</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39190</t>
+          <t>38883</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101233</t>
+          <t>100950</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>119101</t>
+          <t>118821</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>91993</t>
+          <t>92026</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110082</t>
+          <t>110247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>198590</t>
+          <t>198647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>224400</t>
+          <t>223584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,04%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22779</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40231</t>
+          <t>39923</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26349</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>43436</t>
+          <t>43507</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>52051</t>
+          <t>53004</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>76540</t>
+          <t>77195</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28795</t>
+          <t>28153</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40189</t>
+          <t>40263</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44456</t>
+          <t>44665</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56976</t>
+          <t>57520</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>76840</t>
+          <t>76789</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>94164</t>
+          <t>93992</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,46%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21217</t>
+          <t>21751</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>13664</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26008</t>
+          <t>25968</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27011</t>
+          <t>27103</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43661</t>
+          <t>43612</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>444315</t>
+          <t>444799</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>485412</t>
+          <t>483497</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>484962</t>
+          <t>485477</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>525077</t>
+          <t>524672</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>943922</t>
+          <t>942752</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>999597</t>
+          <t>997901</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>146769</t>
+          <t>147468</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>184990</t>
+          <t>185592</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>152881</t>
+          <t>154815</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>189880</t>
+          <t>190182</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>310415</t>
+          <t>309793</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>363954</t>
+          <t>362694</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36554</t>
+          <t>37169</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>58087</t>
+          <t>59223</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>30380</t>
+          <t>30505</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>51149</t>
+          <t>52278</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>71656</t>
+          <t>73261</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>103204</t>
+          <t>101882</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54861</t>
+          <t>55440</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68179</t>
+          <t>68402</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70553</t>
+          <t>70566</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83804</t>
+          <t>83973</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129812</t>
+          <t>129911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147945</t>
+          <t>147536</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>19032</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24389</t>
+          <t>23933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23371</t>
+          <t>22670</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39228</t>
+          <t>37889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>10125</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>20192</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72454</t>
+          <t>72854</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86752</t>
+          <t>86739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75278</t>
+          <t>74242</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89920</t>
+          <t>90165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152448</t>
+          <t>152107</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173333</t>
+          <t>172477</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>16085</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29524</t>
+          <t>29793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>33806</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>57823</t>
+          <t>58494</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38480</t>
+          <t>38641</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50226</t>
+          <t>50499</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48312</t>
+          <t>47350</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61377</t>
+          <t>60666</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90397</t>
+          <t>90327</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>107359</t>
+          <t>107470</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,29%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20049</t>
+          <t>20328</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11863</t>
+          <t>12562</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24597</t>
+          <t>25577</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24332</t>
+          <t>24769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40974</t>
+          <t>41124</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>154241</t>
+          <t>155733</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>175569</t>
+          <t>176228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139870</t>
+          <t>139543</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159977</t>
+          <t>160937</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>300053</t>
+          <t>301348</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>332129</t>
+          <t>331755</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,37%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37673</t>
+          <t>37914</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57122</t>
+          <t>56612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39271</t>
+          <t>38665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58716</t>
+          <t>59648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81061</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110165</t>
+          <t>109101</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17604</t>
+          <t>18123</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16100</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31704</t>
+          <t>30931</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87423</t>
+          <t>86564</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104147</t>
+          <t>104706</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86881</t>
+          <t>87935</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106547</t>
+          <t>106259</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>181729</t>
+          <t>181867</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>206479</t>
+          <t>205927</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,73%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>24806</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41295</t>
+          <t>41080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>27096</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44029</t>
+          <t>43740</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>55564</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>79162</t>
+          <t>78701</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12353</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25916</t>
+          <t>26252</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34647</t>
+          <t>34664</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46312</t>
+          <t>46100</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40924</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53731</t>
+          <t>53321</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>80368</t>
+          <t>79598</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97474</t>
+          <t>96535</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,57%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>20930</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>21159</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>22887</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37433</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>470797</t>
+          <t>471851</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>508205</t>
+          <t>509150</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>490987</t>
+          <t>490640</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>531491</t>
+          <t>529658</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>974203</t>
+          <t>972431</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1029983</t>
+          <t>1027260</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>128134</t>
+          <t>127312</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>162606</t>
+          <t>160504</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>139980</t>
+          <t>141162</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>177991</t>
+          <t>179100</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>276653</t>
+          <t>278275</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>325784</t>
+          <t>328237</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28028</t>
+          <t>28243</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46733</t>
+          <t>48274</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29729</t>
+          <t>30026</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>50130</t>
+          <t>50518</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>62363</t>
+          <t>63301</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>90034</t>
+          <t>91519</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76898</t>
+          <t>76705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90726</t>
+          <t>90233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101971</t>
+          <t>102116</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121445</t>
+          <t>120961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>184008</t>
+          <t>183618</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>208001</t>
+          <t>207518</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,31%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>21853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>29314</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22437</t>
+          <t>22479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44294</t>
+          <t>44236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>18672</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65878</t>
+          <t>65807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79790</t>
+          <t>79628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64562</t>
+          <t>64571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80025</t>
+          <t>79486</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135707</t>
+          <t>135651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155788</t>
+          <t>155285</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23314</t>
+          <t>23606</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>24712</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>25205</t>
+          <t>25182</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43860</t>
+          <t>44043</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>12260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17388</t>
+          <t>17686</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34872</t>
+          <t>34569</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45117</t>
+          <t>44872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44172</t>
+          <t>43230</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56105</t>
+          <t>56233</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81176</t>
+          <t>82555</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>98189</t>
+          <t>99315</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14079</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30396</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>104816</t>
+          <t>100225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>182369</t>
+          <t>182472</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>161441</t>
+          <t>161917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>184208</t>
+          <t>184944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>257295</t>
+          <t>269754</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>357024</t>
+          <t>358694</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28898</t>
+          <t>28453</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108763</t>
+          <t>111023</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>21097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40686</t>
+          <t>40980</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56983</t>
+          <t>56703</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>159397</t>
+          <t>151013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22935</t>
+          <t>24126</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31035</t>
+          <t>29176</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83305</t>
+          <t>82557</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>98219</t>
+          <t>98258</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125581</t>
+          <t>124701</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>144145</t>
+          <t>145007</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>215249</t>
+          <t>213671</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>239707</t>
+          <t>238936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13089</t>
+          <t>13929</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26683</t>
+          <t>27428</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25840</t>
+          <t>26161</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26515</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>47344</t>
+          <t>48390</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14663</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,82 +13076,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9353</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>4744</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>16669</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>10,25%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>18063</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>11420</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>26238</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>4,05%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>9353</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>4602</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>15645</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>9,62%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>18063</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>12388</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>26959</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52896</t>
+          <t>53035</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63507</t>
+          <t>63274</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>51457</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62792</t>
+          <t>63073</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>108153</t>
+          <t>109157</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>124161</t>
+          <t>124655</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,47%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15144</t>
+          <t>15222</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15756</t>
+          <t>16455</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13058</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26611</t>
+          <t>27452</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>424248</t>
+          <t>432333</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>532360</t>
+          <t>533311</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>583732</t>
+          <t>582470</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>625832</t>
+          <t>624842</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1021098</t>
+          <t>1032529</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1145195</t>
+          <t>1146834</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>96004</t>
+          <t>95106</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>210625</t>
+          <t>200564</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>84598</t>
+          <t>86384</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>120503</t>
+          <t>123214</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>191988</t>
+          <t>191981</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>318926</t>
+          <t>311916</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13950,7 +13950,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19540</t>
+          <t>19818</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>37585</t>
+          <t>37880</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54564</t>
+          <t>54004</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>55354</t>
+          <t>55902</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>82562</t>
+          <t>85469</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
